--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>システム名</t>
   </si>
@@ -43,6 +43,9 @@
     <t>故障状況</t>
   </si>
   <si>
+    <t>ステージ</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -409,34 +412,40 @@
     <t>備考</t>
   </si>
   <si>
-    <t>区分</t>
-  </si>
-  <si>
-    <t>結果コード</t>
-  </si>
-  <si>
-    <t>ステージ</t>
+    <t>値</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>正常な動作・入力に対するテスト</t>
+  </si>
+  <si>
+    <t>異常な入力・エラーケースに対するテスト</t>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>境界値・パフォーマンス等</t>
   </si>
   <si>
     <t>OK</t>
   </si>
   <si>
+    <t>期待される挙動と一致</t>
+  </si>
+  <si>
     <t>NG</t>
   </si>
   <si>
-    <t>その他</t>
+    <t>期待される挙動と不一致</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>正常動作</t>
-  </si>
-  <si>
-    <t>不具合あり</t>
-  </si>
-  <si>
-    <t>未確認</t>
+    <t>未実施</t>
   </si>
 </sst>
 </file>
@@ -465,26 +474,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F497D" tint="0"/>
+        <fgColor rgb="FF002060" tint="0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4" tint="0"/>
+        <fgColor rgb="FF00467F" tint="0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA" tint="0"/>
+        <fgColor rgb="FFC6EFCE" tint="0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEBEB" tint="0"/>
+        <fgColor rgb="FFFFC7CE" tint="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -492,38 +501,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="5" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="3" applyFill="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="5" applyFill="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,19 +521,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="1" max="1" width="11.9720973968506" customWidth="1"/>
+    <col min="2" max="2" width="10.9265241622925" customWidth="1"/>
+    <col min="3" max="3" width="11.8295488357544" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.2795743942261" customWidth="1"/>
+    <col min="6" max="6" width="55.1260185241699" customWidth="1"/>
+    <col min="7" max="7" width="52.9734878540039" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="12.0201816558838" customWidth="1"/>
+    <col min="10" max="10" width="12.0201816558838" customWidth="1"/>
+    <col min="11" max="11" width="12.0201816558838" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,179 +555,194 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="0" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="s">
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="K7" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>1</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>22</v>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>2</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>22</v>
+      <c r="G9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>3</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>22</v>
+      <c r="G10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>4</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>22</v>
+      <c r="G11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>35</v>
+      <c r="B12" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>36</v>
@@ -747,759 +750,831 @@
       <c r="D12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>6</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>22</v>
+      <c r="G13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>7</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>22</v>
+      <c r="G14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>8</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>22</v>
+      <c r="G15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>9</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>22</v>
+      <c r="G16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>22</v>
+      <c r="G17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>11</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>22</v>
+      <c r="G18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>35</v>
+      <c r="B19" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>35</v>
+      <c r="B20" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>14</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>22</v>
+      <c r="G21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>15</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="E22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>22</v>
+      <c r="G22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>16</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>22</v>
+      <c r="G23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4">
         <v>17</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>35</v>
+      <c r="B24" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="E24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>84</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4">
-        <v>18</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="A25" s="3">
+        <v>18</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>22</v>
+      <c r="G25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4">
         <v>19</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>35</v>
+      <c r="B26" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>20</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>21</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
         <v>22</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4">
-        <v>20</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4">
-        <v>21</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4">
-        <v>22</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="E29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>22</v>
+      <c r="G29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4">
-        <v>23</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="A30" s="3">
+        <v>23</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="E30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>22</v>
+      <c r="G30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>24</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>22</v>
+      <c r="G31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>25</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>22</v>
+      <c r="G32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>26</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>22</v>
+      <c r="G33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>27</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="E34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>22</v>
+      <c r="G34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>28</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>22</v>
+      <c r="G35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1512,32 +1587,32 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.9265241622925" customWidth="1"/>
+    <col min="3" max="3" width="10.9265241622925" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.9265241622925" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>130</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1550,86 +1625,86 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="1" width="10.9060640335083" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.483814239502" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="0" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>138</v>
       </c>
+      <c r="C5" s="0" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>139</v>
+      <c r="A6" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>140</v>
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>システム名</t>
   </si>
@@ -73,6 +73,9 @@
     <t>正常系</t>
   </si>
   <si>
+    <t>共通</t>
+  </si>
+  <si>
     <t>S-01</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
     <t>タイトルに戻った際、アイテム選択枠が完全に消えている</t>
   </si>
   <si>
+    <t>初級</t>
+  </si>
+  <si>
     <t>L-01</t>
   </si>
   <si>
@@ -244,6 +250,9 @@
     <t>「空の箱だ」と表示され、2本目は手に入らない</t>
   </si>
   <si>
+    <t>中級</t>
+  </si>
+  <si>
     <t>M-01</t>
   </si>
   <si>
@@ -320,6 +329,9 @@
   </si>
   <si>
     <t>金庫が明るく（解錠マーク）なっている</t>
+  </si>
+  <si>
+    <t>上級</t>
   </si>
   <si>
     <t>H-01</t>
@@ -605,31 +617,31 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -640,31 +652,31 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -675,31 +687,31 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -710,31 +722,31 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -742,34 +754,34 @@
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -780,31 +792,31 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -815,31 +827,31 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -850,31 +862,31 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -885,31 +897,31 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -920,31 +932,31 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -955,31 +967,31 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -987,34 +999,34 @@
         <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1022,34 +1034,34 @@
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -1060,31 +1072,31 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1095,31 +1107,31 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1130,31 +1142,31 @@
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -1162,34 +1174,34 @@
         <v>17</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -1200,31 +1212,31 @@
         <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1232,34 +1244,34 @@
         <v>19</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1270,31 +1282,31 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -1305,31 +1317,31 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1340,31 +1352,31 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -1375,31 +1387,31 @@
         <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -1410,31 +1422,31 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1445,31 +1457,31 @@
         <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -1480,31 +1492,31 @@
         <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -1515,31 +1527,31 @@
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -1550,31 +1562,31 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1600,19 +1612,19 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1635,10 +1647,10 @@
         <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
@@ -1649,7 +1661,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -1657,10 +1669,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -1668,10 +1680,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -1679,10 +1691,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -1690,10 +1702,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -1701,10 +1713,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -1,20 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\テスト\脱出ゲーム\docs\テスト仕様書\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF9549B-1533-44AE-A8E0-B773DCE24AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="脱出ゲーム" sheetId="1" r:id="rId1"/>
-    <sheet name="故障一覧" sheetId="2" r:id="rId3"/>
-    <sheet name="マスタ" sheetId="3" r:id="rId4"/>
+    <sheet name="故障一覧" sheetId="2" r:id="rId2"/>
+    <sheet name="マスタ" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>システム名</t>
   </si>
@@ -424,48 +432,24 @@
     <t>備考</t>
   </si>
   <si>
-    <t>値</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>正常な動作・入力に対するテスト</t>
-  </si>
-  <si>
-    <t>異常な入力・エラーケースに対するテスト</t>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>NG</t>
   </si>
   <si>
     <t>その他</t>
   </si>
   <si>
-    <t>境界値・パフォーマンス等</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>期待される挙動と一致</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>期待される挙動と不一致</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>未実施</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -473,11 +457,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF" tint="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,26 +475,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060" tint="0"/>
+        <fgColor rgb="FF002060"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00467F" tint="0"/>
+        <fgColor rgb="FF00467F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE" tint="0"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE" tint="0"/>
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3D3D3" tint="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -513,1213 +507,1499 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="3" applyFill="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="5" applyFill="1" xfId="0" applyProtection="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="5" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.9720973968506" customWidth="1"/>
-    <col min="2" max="2" width="10.9265241622925" customWidth="1"/>
-    <col min="3" max="3" width="11.8295488357544" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.2795743942261" customWidth="1"/>
-    <col min="6" max="6" width="55.1260185241699" customWidth="1"/>
-    <col min="7" max="7" width="52.9734878540039" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.0201816558838" customWidth="1"/>
-    <col min="10" max="10" width="12.0201816558838" customWidth="1"/>
-    <col min="11" max="11" width="12.0201816558838" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1" style="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1" style="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1" style="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1" style="1"/>
+    <col min="5" max="5" width="13.21875" customWidth="1" style="1"/>
+    <col min="6" max="6" width="55.109375" customWidth="1" style="1"/>
+    <col min="7" max="7" width="53" customWidth="1" style="1"/>
+    <col min="8" max="8" width="9.109375" customWidth="1" style="1"/>
+    <col min="9" max="11" width="12" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="H8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3">
+      <c r="A9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="H9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3">
+      <c r="A10" s="5">
         <v>3</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="H10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3">
+      <c r="A11" s="5">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="H11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="6">
         <v>5</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="H12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3">
+      <c r="A13" s="5">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="H13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3">
+      <c r="A14" s="5">
         <v>7</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="H14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3">
+      <c r="A15" s="5">
         <v>8</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="H15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3">
+      <c r="A16" s="5">
         <v>9</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="H16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3">
+      <c r="A17" s="5">
         <v>10</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="3" t="s">
+      <c r="H17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3">
+      <c r="A18" s="5">
         <v>11</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="3" t="s">
+      <c r="H18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4">
+      <c r="A19" s="6">
         <v>12</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="4" t="s">
+      <c r="H19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4">
+      <c r="A20" s="6">
         <v>13</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="4" t="s">
+      <c r="H20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3">
+      <c r="A21" s="5">
         <v>14</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="H21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3">
+      <c r="A22" s="5">
         <v>15</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="H22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3">
+      <c r="A23" s="5">
         <v>16</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="3" t="s">
+      <c r="H23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4">
+      <c r="A24" s="6">
         <v>17</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K24" s="4" t="s">
+      <c r="H24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3">
-        <v>18</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="A25" s="5">
+        <v>18</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K25" s="3" t="s">
+      <c r="H25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4">
+      <c r="A26" s="6">
         <v>19</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="4" t="s">
+      <c r="H26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3">
+      <c r="A27" s="5">
         <v>20</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" s="3" t="s">
+      <c r="H27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3">
+      <c r="A28" s="5">
         <v>21</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" s="3" t="s">
+      <c r="H28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3">
+      <c r="A29" s="5">
         <v>22</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="H29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3">
+      <c r="A30" s="5">
         <v>23</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K30" s="3" t="s">
+      <c r="H30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3">
-        <v>24</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="A31" s="5">
+        <v>24</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K31" s="3" t="s">
+      <c r="H31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3">
+      <c r="A32" s="5">
         <v>25</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K32" s="3" t="s">
+      <c r="H32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3">
+      <c r="A33" s="5">
         <v>26</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K33" s="3" t="s">
+      <c r="H33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3">
+      <c r="A34" s="5">
         <v>27</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K34" s="3" t="s">
+      <c r="H34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3">
+      <c r="A35" s="5">
         <v>28</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K35" s="3" t="s">
+      <c r="H35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
+  <dataValidations count="3">
+    <dataValidation type="list" sqref="B8:B35" showErrorMessage="1" error="正常系/異常系/その他 から選択してください" errorTitle="入力エラー">
+      <formula1>マスタ!$A$2:$A$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H8:H35" showErrorMessage="1" error="OK/NG/- から選択してください" errorTitle="入力エラー">
+      <formula1>マスタ!$B$2:$B$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I8:I35" showErrorMessage="1" error="OK/NG/- から選択してください" errorTitle="入力エラー">
+      <formula1>マスタ!$B$2:$B$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.9265241622925" customWidth="1"/>
-    <col min="3" max="3" width="10.9265241622925" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="10.9265241622925" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1" style="1"/>
+    <col min="2" max="3" width="10.88671875" customWidth="1" style="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1" style="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1" style="1"/>
+    <col min="6" max="6" width="9.109375" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>135</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.9060640335083" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="38.483814239502" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="0" t="s">
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>147</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>システム名</t>
   </si>
@@ -40,7 +40,10 @@
     <t>項番</t>
   </si>
   <si>
-    <t>故障状況</t>
+    <t>正常/異常</t>
+  </si>
+  <si>
+    <t>テスト種別</t>
   </si>
   <si>
     <t>ステージ</t>
@@ -52,7 +55,7 @@
     <t>カテゴリ</t>
   </si>
   <si>
-    <t>確認内容</t>
+    <t>確認内容・手順</t>
   </si>
   <si>
     <t>期待される挙動</t>
@@ -73,6 +76,9 @@
     <t>正常系</t>
   </si>
   <si>
+    <t>WB</t>
+  </si>
+  <si>
     <t>V</t>
   </si>
   <si>
@@ -314,6 +320,96 @@
   </si>
   <si>
     <t>is-active クラスを除去、フォーカス処理なし</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>UI-BB01</t>
+  </si>
+  <si>
+    <t>画面操作</t>
+  </si>
+  <si>
+    <t>ブラウザで index.html を開き、「BEGINNER（初級）」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>タイトル画面が非表示になり、ゲームフィールドと第1部屋・第1視点が表示される</t>
+  </si>
+  <si>
+    <t>UI-BB02</t>
+  </si>
+  <si>
+    <t>準備中の難易度ボタン（例：ELITE）をクリックする</t>
+  </si>
+  <si>
+    <t>「準備中の難易度です。」メッセージが表示され、タイトル画面のまま推移しない</t>
+  </si>
+  <si>
+    <t>UI-BB03</t>
+  </si>
+  <si>
+    <t>ゲーム中、部屋の右矢印ボタン（→）をクリックする</t>
+  </si>
+  <si>
+    <t>視点が右に移動し、次の視点のオブジェクトが表示される</t>
+  </si>
+  <si>
+    <t>UI-BB04</t>
+  </si>
+  <si>
+    <t>ゲーム中、最右端の視点から右矢印ボタン（→）をクリックする</t>
+  </si>
+  <si>
+    <t>視点が先頭（0番）に循環し、先頭視点のオブジェクトが表示される</t>
+  </si>
+  <si>
+    <t>UI-BB05</t>
+  </si>
+  <si>
+    <t>ゲーム中、画面内のアイテムオブジェクトをクリックする</t>
+  </si>
+  <si>
+    <t>インベントリスロットにアイテムアイコンが追加され、取得メッセージがナレーターエリアに表示される</t>
+  </si>
+  <si>
+    <t>UI-BB06</t>
+  </si>
+  <si>
+    <t>既に所持しているアイテムオブジェクトを再度クリックする</t>
+  </si>
+  <si>
+    <t>インベントリにアイテムが重複追加されない（スロット数・アイテム数が変わらない）</t>
+  </si>
+  <si>
+    <t>UI-BB07</t>
+  </si>
+  <si>
+    <t>鍵のかかったオブジェクトをクリックしてモーダルを開き、正解コードを入力して「解鍵」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>「ロック解除！」メッセージが表示され、オブジェクトの状態が開鍵に変わる</t>
+  </si>
+  <si>
+    <t>UI-BB08</t>
+  </si>
+  <si>
+    <t>解鍵モーダルを開いてコード入力欄を空白のまま「解鍵」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>「コードを入力してください。」エラーメッセージが表示される</t>
+  </si>
+  <si>
+    <t>UI-BB09</t>
+  </si>
+  <si>
+    <t>解鍵モーダルに誤ったコードを入力して「解鍵」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>入力欄が赤くハイライト（input-error クラス付与）され、しばらく後に解除される</t>
   </si>
   <si>
     <t>OK</t>
@@ -408,20 +504,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,772 +580,1132 @@
       <c r="K7" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="L7" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4">
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10">
       <c r="A10" s="5">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="11">
       <c r="A11" s="5">
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="4">
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="5">
         <v>6</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
     </row>
     <row r="14">
       <c r="A14" s="5">
         <v>7</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="5">
         <v>8</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
     </row>
     <row r="16">
       <c r="A16" s="4">
         <v>9</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="5">
         <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="5">
         <v>11</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
     </row>
     <row r="19">
       <c r="A19" s="4">
         <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="4"/>
+        <v>52</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="5">
         <v>13</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H20" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
     </row>
     <row r="21">
       <c r="A21" s="5">
         <v>14</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
     </row>
     <row r="22">
       <c r="A22" s="4">
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="5">
         <v>16</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
     </row>
     <row r="24">
       <c r="A24" s="5">
         <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
     </row>
     <row r="25">
       <c r="A25" s="4">
         <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="5">
         <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>74</v>
+      </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
     </row>
     <row r="27">
       <c r="A27" s="4">
         <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="4">
         <v>21</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" s="4"/>
+        <v>79</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="5">
         <v>22</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H29" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
     </row>
     <row r="30">
       <c r="A30" s="4">
         <v>23</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
     </row>
     <row r="31">
       <c r="A31" s="5">
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
     </row>
     <row r="32">
       <c r="A32" s="4">
         <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="4">
         <v>26</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H33" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
     </row>
     <row r="34">
       <c r="A34" s="4">
         <v>27</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H34" s="4"/>
+        <v>97</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="4">
         <v>28</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H35" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4">
+        <v>29</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5">
+        <v>30</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4">
+        <v>32</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4">
+        <v>33</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5">
+        <v>34</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4">
+        <v>35</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5">
+        <v>36</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="B8:B35" showErrorMessage="1">
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="B8:B44" showErrorMessage="1">
       <formula1>マスタ!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H8:H35" showErrorMessage="1">
+    <dataValidation type="list" sqref="C8:C44" showErrorMessage="1">
+      <formula1>マスタ!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I8:I44" showErrorMessage="1">
       <formula1>マスタ!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I8:I35" showErrorMessage="1">
+    <dataValidation type="list" sqref="J8:J44" showErrorMessage="1">
       <formula1>マスタ!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1258,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,6 +1742,9 @@
       </c>
       <c r="H1" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1294,11 +1754,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1306,31 +1767,40 @@
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>100</v>
+        <v>132</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>101</v>
+        <v>133</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>システム名</t>
   </si>
@@ -79,7 +79,7 @@
     <t>WB</t>
   </si>
   <si>
-    <t>V</t>
+    <t>共通</t>
   </si>
   <si>
     <t>V-01</t>
@@ -163,9 +163,6 @@
     <t>false を返す（trim後に空になるため）</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
     <t>G-01</t>
   </si>
   <si>
@@ -325,7 +322,7 @@
     <t>BB</t>
   </si>
   <si>
-    <t>UI</t>
+    <t>初級</t>
   </si>
   <si>
     <t>UI-BB01</t>
@@ -925,19 +922,19 @@
         <v>20</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -955,19 +952,19 @@
         <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -985,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -1015,19 +1012,19 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1045,19 +1042,19 @@
         <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -1075,19 +1072,19 @@
         <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -1105,19 +1102,19 @@
         <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1135,19 +1132,19 @@
         <v>20</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -1165,19 +1162,19 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1195,19 +1192,19 @@
         <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1225,19 +1222,19 @@
         <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
@@ -1255,19 +1252,19 @@
         <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1285,19 +1282,19 @@
         <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
@@ -1315,19 +1312,19 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1345,19 +1342,19 @@
         <v>20</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -1375,19 +1372,19 @@
         <v>20</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -1405,19 +1402,19 @@
         <v>20</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -1432,22 +1429,22 @@
         <v>19</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -1462,22 +1459,22 @@
         <v>26</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -1492,22 +1489,22 @@
         <v>19</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -1522,22 +1519,22 @@
         <v>19</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -1552,22 +1549,22 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -1582,22 +1579,22 @@
         <v>26</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E41" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -1612,22 +1609,22 @@
         <v>19</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -1642,22 +1639,22 @@
         <v>26</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G43" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -1672,22 +1669,22 @@
         <v>26</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -1778,7 +1775,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>20</v>
@@ -1789,18 +1786,18 @@
         <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>134</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
